--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555411921</v>
+        <v>46157.93112618686</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112618686</v>
+        <v>46157.9313649831</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9313649831</v>
+        <v>46157.9338402077</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9338402077</v>
+        <v>46157.9369577599</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9369577599</v>
+        <v>46158.28204941763</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204941763</v>
+        <v>46158.29652254463</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29652254463</v>
+        <v>46158.29807520794</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807520794</v>
+        <v>46158.33370406881</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370406881</v>
+        <v>46158.37221742704</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221742704</v>
+        <v>46158.37275582487</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
